--- a/Supplementary_Data_3.xlsx
+++ b/Supplementary_Data_3.xlsx
@@ -1759,6 +1759,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -1826,6 +1827,7 @@
         <v>11</v>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
@@ -1840,7 +1842,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>-32.74403048033128</v>
+        <v>87.00539999999999</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2129,8 +2131,6 @@
           <t>Bayes factor</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>B_12 = 0.8670 (inconclusive)</t>
@@ -2153,7 +2153,6 @@
           <t>0.995377</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2241,7 +2240,6 @@
           <t>2698</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2392,8 +2390,6 @@
           <t>kappa=0.5802, beta=3708, b=4.15e-05</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2411,7 +2407,6 @@
           <t>4PL fit = 0.9992; R2 limit = 0.9951</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2429,7 +2424,6 @@
           <t>4PL B = 1.014</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">

--- a/Supplementary_Data_3.xlsx
+++ b/Supplementary_Data_3.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Raw_Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_TCS_PerPoint" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_Fit_Parameters" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_Bootstrap_CI" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_Correlations" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_LoB_LoD_LoQ" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_R3_Linear" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_D_Profile_Likelihood" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_Shapiro_Wilk" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Deviance_Residuals" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Kappa_Scan" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Resid_vs_Kappa" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_LOO_PerFold" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_R1_Model" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="1_Raw_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2_TCS_PerPoint" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3_Fit_Parameters" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4_Bootstrap_CI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5_Correlations" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6_LoB_LoD_LoQ" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7_R3_Linear" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8_D_Profile_Likelihood" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9_Shapiro_Wilk" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_Deviance_Residuals" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_Kappa_Scan" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_Resid_vs_Kappa" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13_LOO_PerFold" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14_R1_Model" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -721,12 +721,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>4PL deviance residual</t>
+          <t>4PL quasi-deviance residual</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>TCS deviance residual</t>
+          <t>TCS quasi-deviance residual</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -743,7 +743,7 @@
         <v>-9.580878857183667e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.724148239068845</v>
+        <v>-0.7241474067916032</v>
       </c>
     </row>
     <row r="3">
@@ -751,10 +751,10 @@
         <v>0.35</v>
       </c>
       <c r="B3" t="n">
-        <v>0.09024011720648052</v>
+        <v>0.08995622730251106</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.3668567491847637</v>
+        <v>-0.3668562057882018</v>
       </c>
     </row>
     <row r="4">
@@ -762,10 +762,10 @@
         <v>0.7</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1235518099801233</v>
+        <v>0.1231475407084827</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1969838290522737</v>
+        <v>-0.1969834538283697</v>
       </c>
     </row>
     <row r="5">
@@ -773,10 +773,10 @@
         <v>3.5</v>
       </c>
       <c r="B5" t="n">
-        <v>0.425287840724591</v>
+        <v>0.4245145273212265</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5245428350003876</v>
+        <v>0.524542692461884</v>
       </c>
     </row>
     <row r="6">
@@ -784,10 +784,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.2390047557500909</v>
+        <v>-0.2399502639651473</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1064991823122273</v>
+        <v>0.1064987712892797</v>
       </c>
     </row>
     <row r="7">
@@ -795,10 +795,10 @@
         <v>35</v>
       </c>
       <c r="B7" t="n">
-        <v>2.739200327695625</v>
+        <v>2.737745339220424</v>
       </c>
       <c r="C7" t="n">
-        <v>4.146042834106059</v>
+        <v>4.146041455235562</v>
       </c>
     </row>
     <row r="8">
@@ -806,10 +806,10 @@
         <v>70</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.5739183794833869</v>
+        <v>-0.5754530986252646</v>
       </c>
       <c r="C8" t="n">
-        <v>1.563223018799941</v>
+        <v>1.563221065367245</v>
       </c>
     </row>
     <row r="9">
@@ -817,14 +817,14 @@
         <v>350</v>
       </c>
       <c r="B9" t="n">
-        <v>-4.315651223441447</v>
+        <v>-4.316788414498171</v>
       </c>
       <c r="C9" t="n">
-        <v>1.013436344206959</v>
+        <v>1.013431918209968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>high deviance residual under 4PL</t>
+          <t>high quasi-deviance residual under 4PL</t>
         </is>
       </c>
     </row>
@@ -833,10 +833,10 @@
         <v>700</v>
       </c>
       <c r="B10" t="n">
-        <v>2.945300521446221</v>
+        <v>2.944882930451728</v>
       </c>
       <c r="C10" t="n">
-        <v>10.40172609531794</v>
+        <v>10.40171972733174</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -849,10 +849,10 @@
         <v>3500</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.2446698844937979</v>
+        <v>-0.2430375840503297</v>
       </c>
       <c r="C11" t="n">
-        <v>5.375201232149347</v>
+        <v>5.375188194807635</v>
       </c>
     </row>
     <row r="12">
@@ -860,10 +860,10 @@
         <v>7000</v>
       </c>
       <c r="B12" t="n">
-        <v>0.03371865012382419</v>
+        <v>0.03330392122813915</v>
       </c>
       <c r="C12" t="n">
-        <v>-8.972179886636601</v>
+        <v>-8.972196668153128</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>logL (binomial)</t>
+          <t>quasi-logL (binomial-form)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -927,19 +927,19 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>-98899.783836307</v>
+        <v>-98899.78383612729</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7999178388241917</v>
+        <v>0.799917838845579</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3279147707965151</v>
+        <v>0.3279147707916982</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002316476003022486</v>
+        <v>0.00231647599820544</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3279147707965151</v>
+        <v>0.3279147707916982</v>
       </c>
     </row>
     <row r="3">
@@ -947,19 +947,19 @@
         <v>0.2</v>
       </c>
       <c r="B3" t="n">
-        <v>-97415.3998771694</v>
+        <v>-97415.39987713784</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8915286259501731</v>
+        <v>0.8915286259621026</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2480780045396525</v>
+        <v>0.2480780045344829</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001518459746160009</v>
+        <v>0.001518459740990413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2480780045396525</v>
+        <v>0.2480780045344829</v>
       </c>
     </row>
     <row r="4">
@@ -967,19 +967,19 @@
         <v>0.3</v>
       </c>
       <c r="B4" t="n">
-        <v>-96449.26208791937</v>
+        <v>-96449.26208791936</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9465514115639152</v>
+        <v>0.9465514115637901</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1805263518409379</v>
+        <v>0.1805263518410732</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008457493551376778</v>
+        <v>0.0008457493552728856</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1805263518409379</v>
+        <v>0.1805263518410732</v>
       </c>
     </row>
     <row r="5">
@@ -990,16 +990,16 @@
         <v>-95870.88561428597</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9773101408238279</v>
+        <v>0.9773101408238397</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1226278460435752</v>
+        <v>0.1226278460435224</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0006895211466950357</v>
+        <v>0.0006895211467479712</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1226278460435752</v>
+        <v>0.1226278460435224</v>
       </c>
     </row>
     <row r="6">
@@ -1010,16 +1010,16 @@
         <v>-95586.90507423568</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9917242920847139</v>
+        <v>0.9917242920846605</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07245301126294634</v>
+        <v>0.07245301126315373</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009319392606574658</v>
+        <v>0.0009319392604500093</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07245301126294634</v>
+        <v>0.07245301126315373</v>
       </c>
     </row>
     <row r="7">
@@ -1030,20 +1030,20 @@
         <v>-95525.17550707994</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.9950509195462272</v>
+        <v>0.9950509195461233</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.0371853723142318</v>
+        <v>0.03718537231434649</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.001098603737559563</v>
+        <v>0.001098603737444935</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.0371853723142318</v>
+        <v>0.03718537231434649</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>MLE</t>
+          <t>quasi-MLE</t>
         </is>
       </c>
     </row>
@@ -1052,19 +1052,19 @@
         <v>0.6</v>
       </c>
       <c r="B8" t="n">
-        <v>-95529.05729185305</v>
+        <v>-95529.05729185304</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9950083605035616</v>
+        <v>0.9950083605039928</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02855537178764123</v>
+        <v>0.02855537178727408</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001138714152629302</v>
+        <v>0.001138714152996118</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02855537178764123</v>
+        <v>0.02855537178727408</v>
       </c>
     </row>
     <row r="9">
@@ -1075,16 +1075,16 @@
         <v>-95646.5101133204</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9906569074581755</v>
+        <v>0.990656907459031</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03851716218289031</v>
+        <v>0.03851716218316309</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001314237975471217</v>
+        <v>0.00131423797574397</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03851716218289031</v>
+        <v>0.03851716218316309</v>
       </c>
     </row>
     <row r="10">
@@ -1092,19 +1092,19 @@
         <v>0.8</v>
       </c>
       <c r="B10" t="n">
-        <v>-95900.80086901656</v>
+        <v>-95900.80086901657</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9810315986379311</v>
+        <v>0.981031598620994</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05571188241773817</v>
+        <v>0.05571188241507241</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00146138468090752</v>
+        <v>0.001461384678241746</v>
       </c>
       <c r="F10" t="n">
-        <v>0.05571188241773817</v>
+        <v>0.05571188241507241</v>
       </c>
     </row>
     <row r="11">
@@ -1112,19 +1112,19 @@
         <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>-96708.39490036831</v>
+        <v>-96708.39490036832</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9517348166901102</v>
+        <v>0.9517348166048164</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1030556729604959</v>
+        <v>0.1030556729556314</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001844717753988418</v>
+        <v>0.001844717749124064</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1030556729604959</v>
+        <v>0.1030556729556314</v>
       </c>
     </row>
     <row r="12">
@@ -1135,16 +1135,16 @@
         <v>-99686.69880188449</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8414071042625471</v>
+        <v>0.84140710533639</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2080263273441602</v>
+        <v>0.2080263273570214</v>
       </c>
       <c r="E12" t="n">
-        <v>0.002484222137652849</v>
+        <v>0.002484222150513831</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2080263273441602</v>
+        <v>0.2080263273570214</v>
       </c>
     </row>
     <row r="13">
@@ -1155,16 +1155,16 @@
         <v>-103166.51044411</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6332589926079528</v>
+        <v>0.6332589914385198</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2774707368892096</v>
+        <v>0.2774707368838093</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002374531682702265</v>
+        <v>0.002374531677301841</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2774707368892096</v>
+        <v>0.2774707368838093</v>
       </c>
     </row>
     <row r="14">
@@ -1175,16 +1175,16 @@
         <v>-121030.8237391844</v>
       </c>
       <c r="C14" t="n">
-        <v>-11.71538404909864</v>
+        <v>-11.71538428213823</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4422829115979264</v>
+        <v>0.4422829114820632</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01216759663157906</v>
+        <v>0.01216759674744221</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4422829115979264</v>
+        <v>0.4422829114820632</v>
       </c>
     </row>
     <row r="15">
@@ -1195,16 +1195,16 @@
         <v>-136521.893248692</v>
       </c>
       <c r="C15" t="n">
-        <v>-81.78320286981503</v>
+        <v>-81.78320277255442</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5027859399655507</v>
+        <v>0.5027859399841756</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03149769762001543</v>
+        <v>0.03149769760139034</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5027859399655507</v>
+        <v>0.5027859399841756</v>
       </c>
     </row>
   </sheetData>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>κ=0.579 (MLE)</t>
+          <t>κ=0.579 (quasi-MLE)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.454513202547366e-06</v>
+        <v>6.45451306732053e-06</v>
       </c>
       <c r="C2" t="n">
-        <v>1.114156718923263e-06</v>
+        <v>1.114156771770814e-06</v>
       </c>
       <c r="D2" t="n">
-        <v>-7.384395985427563e-06</v>
+        <v>-7.384396192822658e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.710672547421093e-05</v>
+        <v>-1.710672558890109e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.836019097550536e-05</v>
+        <v>-3.836019070270796e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0001403668392098749</v>
+        <v>-0.0001403668440740921</v>
       </c>
     </row>
     <row r="3">
@@ -1286,22 +1286,22 @@
         <v>0.35</v>
       </c>
       <c r="B3" t="n">
-        <v>3.568807761946324e-06</v>
+        <v>3.568807626602975e-06</v>
       </c>
       <c r="C3" t="n">
-        <v>1.123643585923022e-06</v>
+        <v>1.123643638772565e-06</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.865742451714747e-06</v>
+        <v>-4.865742659117134e-06</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.282420387666693e-05</v>
+        <v>-1.282420399136091e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.170879234381923e-05</v>
+        <v>-3.170879207101338e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0001290661023428277</v>
+        <v>-0.0001290661072071731</v>
       </c>
     </row>
     <row r="4">
@@ -1309,22 +1309,22 @@
         <v>0.7</v>
       </c>
       <c r="B4" t="n">
-        <v>6.845196700850493e-07</v>
+        <v>6.845195348472539e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>1.134547801921967e-06</v>
+        <v>1.134547854773503e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.345671569065676e-06</v>
+        <v>-2.345671776475341e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>-8.540264930059129e-06</v>
+        <v>-8.540265044756931e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.505597636314373e-05</v>
+        <v>-2.505597609032942e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0001177639481269454</v>
+        <v>-0.0001177639529911969</v>
       </c>
     </row>
     <row r="5">
@@ -1332,22 +1332,22 @@
         <v>3.5</v>
       </c>
       <c r="B5" t="n">
-        <v>-3.508342406012229e-06</v>
+        <v>-3.508342541293881e-06</v>
       </c>
       <c r="C5" t="n">
-        <v>2.010322418731167e-05</v>
+        <v>2.01032242401791e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>3.669633814950239e-05</v>
+        <v>3.669633794214553e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>4.461268929981539e-05</v>
+        <v>4.461268918519798e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>4.704799413989192e-05</v>
+        <v>4.704799441266282e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>-8.465271741547756e-06</v>
+        <v>-8.465276605824977e-06</v>
       </c>
     </row>
     <row r="6">
@@ -1355,22 +1355,22 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0001075005474853979</v>
+        <v>-0.0001075005476207344</v>
       </c>
       <c r="C6" t="n">
-        <v>-5.493705781525228e-05</v>
+        <v>-5.49370577623649e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.325227718621707e-05</v>
+        <v>-1.325227739364674e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>1.230275460313113e-05</v>
+        <v>1.230275448836442e-05</v>
       </c>
       <c r="F6" t="n">
-        <v>3.842682978440638e-05</v>
+        <v>3.84268300572619e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>2.940694625602931e-05</v>
+        <v>2.940694139180354e-05</v>
       </c>
     </row>
     <row r="7">
@@ -1378,22 +1378,22 @@
         <v>35</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0004053422724094608</v>
+        <v>0.0004053422722741307</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0006895211466950357</v>
+        <v>0.0006895211467479712</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0009319392606574658</v>
+        <v>0.0009319392604500093</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001098603737559563</v>
+        <v>0.001098603737444935</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001314237975471217</v>
+        <v>0.00131423797574397</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001677165150766212</v>
+        <v>0.001677165145901966</v>
       </c>
     </row>
     <row r="8">
@@ -1401,22 +1401,22 @@
         <v>70</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.0008457493551376778</v>
+        <v>-0.0008457493552728856</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.000272051250082739</v>
+        <v>-0.00027205125002994</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0002212835305462771</v>
+        <v>0.0002212835303388727</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0005643348138394313</v>
+        <v>0.0005643348137247556</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001016856755163966</v>
+        <v>0.001016856755436783</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001844717753988418</v>
+        <v>0.001844717749124064</v>
       </c>
     </row>
     <row r="9">
@@ -1424,22 +1424,22 @@
         <v>350</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.006330029134827601</v>
+        <v>-0.006330029134962875</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.003440177183618817</v>
+        <v>-0.003440177183565901</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0009395090696564315</v>
+        <v>-0.0009395090698638767</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0008146366647647646</v>
+        <v>0.0008146366646500855</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003162260233392594</v>
+        <v>0.003162260233665389</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007709591820452354</v>
+        <v>0.00770959181558813</v>
       </c>
     </row>
     <row r="10">
@@ -1447,22 +1447,22 @@
         <v>700</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.00206835522392726</v>
+        <v>-0.002068355224062596</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003716689034973686</v>
+        <v>0.003716689035026477</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00872652381560271</v>
+        <v>0.008726523815395348</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01224453761393428</v>
+        <v>0.01224453761381951</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01696103821669102</v>
+        <v>0.01696103821696378</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02615770803904485</v>
+        <v>0.02615770803418058</v>
       </c>
     </row>
     <row r="11">
@@ -1470,22 +1470,22 @@
         <v>3500</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.05680906383691359</v>
+        <v>-0.05680906383704892</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.02786248111647421</v>
+        <v>-0.0278624811164212</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.002779313002511719</v>
+        <v>-0.00277931300271933</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01484964530710109</v>
+        <v>0.01484964530698635</v>
       </c>
       <c r="F11" t="n">
-        <v>0.03851716218289031</v>
+        <v>0.03851716218316309</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08490853788759706</v>
+        <v>0.08490853788273284</v>
       </c>
     </row>
     <row r="12">
@@ -1493,22 +1493,22 @@
         <v>7000</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.1805263518409379</v>
+        <v>-0.1805263518410732</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.1226278460435752</v>
+        <v>-0.1226278460435224</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.07245301126294634</v>
+        <v>-0.07245301126315373</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0371853723142318</v>
+        <v>-0.03718537231434649</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01017091490284783</v>
+        <v>0.0101709149031205</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1030556729604959</v>
+        <v>0.1030556729556314</v>
       </c>
     </row>
   </sheetData>
@@ -1538,17 +1538,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>logL (4PL hold-out)</t>
+          <t>quasi-logL (4PL hold-out)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>logL (TCS hold-out)</t>
+          <t>quasi-logL (TCS hold-out)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ΔlogL (4PL - TCS)</t>
+          <t>Δ quasi-logL (4PL - TCS)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1568,10 +1568,10 @@
         <v>-12.78185841107558</v>
       </c>
       <c r="D2" t="n">
-        <v>-12.85613109110254</v>
+        <v>-12.85614425164941</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07427268002695975</v>
+        <v>0.07428584057383425</v>
       </c>
     </row>
     <row r="3">
@@ -1582,13 +1582,13 @@
         <v>0.35</v>
       </c>
       <c r="C3" t="n">
-        <v>-32.34951838943137</v>
+        <v>-32.34951217045948</v>
       </c>
       <c r="D3" t="n">
-        <v>-32.49948140166959</v>
+        <v>-32.4994824103166</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1499630122382243</v>
+        <v>0.1499702398571259</v>
       </c>
     </row>
     <row r="4">
@@ -1599,13 +1599,13 @@
         <v>0.7</v>
       </c>
       <c r="C4" t="n">
-        <v>-51.36260462531047</v>
+        <v>-51.36260205789224</v>
       </c>
       <c r="D4" t="n">
-        <v>-51.38830878843746</v>
+        <v>-51.38830879807018</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02570416312698853</v>
+        <v>0.02570674017794516</v>
       </c>
     </row>
     <row r="5">
@@ -1616,13 +1616,13 @@
         <v>3.5</v>
       </c>
       <c r="C5" t="n">
-        <v>-193.463513199758</v>
+        <v>-193.4633967289337</v>
       </c>
       <c r="D5" t="n">
-        <v>-193.4999507415951</v>
+        <v>-193.4999508787046</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03643754183707415</v>
+        <v>0.03655414977092164</v>
       </c>
     </row>
     <row r="6">
@@ -1633,13 +1633,13 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>-313.2606028470516</v>
+        <v>-313.2606457476047</v>
       </c>
       <c r="D6" t="n">
-        <v>-313.2206297234745</v>
+        <v>-313.2206297693284</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0399731235771128</v>
+        <v>-0.04001597827630121</v>
       </c>
     </row>
     <row r="7">
@@ -1650,13 +1650,13 @@
         <v>35</v>
       </c>
       <c r="C7" t="n">
-        <v>-1525.246222433546</v>
+        <v>-1525.179543348388</v>
       </c>
       <c r="D7" t="n">
-        <v>-1527.989953367359</v>
+        <v>-1527.989954001307</v>
       </c>
       <c r="E7" t="n">
-        <v>2.743730933813595</v>
+        <v>2.810410652918563</v>
       </c>
     </row>
     <row r="8">
@@ -1667,13 +1667,13 @@
         <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>-2280.867487869711</v>
+        <v>-2280.867148166323</v>
       </c>
       <c r="D8" t="n">
-        <v>-2281.822563565258</v>
+        <v>-2281.822565021032</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9550756955477482</v>
+        <v>0.9554168547088011</v>
       </c>
     </row>
     <row r="9">
@@ -1684,13 +1684,13 @@
         <v>350</v>
       </c>
       <c r="C9" t="n">
-        <v>-7836.906823548799</v>
+        <v>-7836.908491031558</v>
       </c>
       <c r="D9" t="n">
-        <v>-7818.928941868426</v>
+        <v>-7818.928943974513</v>
       </c>
       <c r="E9" t="n">
-        <v>-17.97788168037368</v>
+        <v>-17.97954705704433</v>
       </c>
     </row>
     <row r="10">
@@ -1701,13 +1701,13 @@
         <v>700</v>
       </c>
       <c r="C10" t="n">
-        <v>-14292.21854829563</v>
+        <v>-14292.21765187804</v>
       </c>
       <c r="D10" t="n">
-        <v>-14344.90456152595</v>
+        <v>-14344.904595642</v>
       </c>
       <c r="E10" t="n">
-        <v>52.68601323032271</v>
+        <v>52.68694376395979</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1723,13 +1723,13 @@
         <v>3500</v>
       </c>
       <c r="C11" t="n">
-        <v>-32192.05301879073</v>
+        <v>-32192.05403611658</v>
       </c>
       <c r="D11" t="n">
-        <v>-32223.59603011685</v>
+        <v>-32223.59605741765</v>
       </c>
       <c r="E11" t="n">
-        <v>31.5430113261209</v>
+        <v>31.54202130106933</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1745,21 +1745,20 @@
         <v>7000</v>
       </c>
       <c r="C12" t="n">
-        <v>-36712.97738093726</v>
+        <v>-36712.97326816854</v>
       </c>
       <c r="D12" t="n">
-        <v>-36905.20413258117</v>
+        <v>-36905.20413489403</v>
       </c>
       <c r="E12" t="n">
-        <v>192.2267516439024</v>
+        <v>192.2308667254911</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>leverage fold (7000 aM, 73% of AICc gap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t>leverage fold (7000 aM, 73% of total LOO quasi-score gap)</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -1774,7 +1773,12 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>23.85664594754417</v>
+        <v>23.86296483938243</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Positive = 4PL higher; negative = TCS higher</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1784,7 +1788,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>17.78483586373025</v>
+        <v>17.7845117044825</v>
       </c>
     </row>
     <row r="17">
@@ -1794,11 +1798,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.34140377399808</v>
+        <v>1.341783526919543</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>n.s. (|t|&lt;2)</t>
+          <t>paired test on predictive quasi-scores</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1813,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.1499630122382243</v>
+        <v>0.1499702398571259</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1827,7 +1831,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
@@ -1838,15 +1841,15 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Margin (±logL)</t>
+          <t>Margin (±quasi-logL)</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>87.00539999999999</v>
+        <v>-32.75379218252783</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1% of mean per-fold |logL|</t>
+          <t>1% of mean per-fold |quasi-logL|</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1861,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>[-8.378, 56.091]</t>
+          <t>[-8.371, 56.097]</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1872,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.00263102545230931</v>
+        <v>0.002632299115951198</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1880,15 +1883,15 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Smallest passing margin (logL)</t>
+          <t>Smallest passing margin (quasi-logL)</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>56.09096952614205</v>
+        <v>56.09670089192942</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.645% of per-fold |logL|</t>
+          <t>0.645% of per-fold |quasi-logL|</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1919,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Method: dynesty nested sampling, nlive=500, bound=multi</t>
+          <t>Method: dynesty nested sampling of the binomial-form quasi-likelihood, nlive=500, bound=multi; logZ and Bayes factors below are descriptive quasi-evidence measures, not exact integer-count Bayesian evidence</t>
         </is>
       </c>
     </row>
@@ -1938,7 +1941,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>R1 95% CI</t>
+          <t>R1 nominal 95% interval (quasi)</t>
         </is>
       </c>
     </row>
@@ -1955,12 +1958,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.5832</t>
+          <t>0.5834</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[0.5656, 0.6163]</t>
+          <t>[0.5661, 0.6172]</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1980,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1343.39</t>
+          <t>1184.39</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>[1.00, 80484.12]</t>
+          <t>[1.00, 80425.05]</t>
         </is>
       </c>
     </row>
@@ -1999,12 +2002,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.000042</t>
+          <t>0.000043</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[0.000009, 0.000095]</t>
+          <t>[0.000011, 0.000096]</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2043,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>logL (MLE)</t>
+          <t>quasi-logL (quasi-MLE)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2050,12 +2053,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-95520.04</t>
+          <t>-95520.02</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>5.15</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2087,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AICc</t>
+          <t>AICc (descriptive, quasi)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2094,46 +2097,48 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>191049.51</t>
+          <t>191049.48</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Δ = -6.34</t>
+          <t>Δ = -6.37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>logZ (nested)</t>
+          <t>quasi-logZ (nested)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-95543.41</t>
+          <t>-95543.32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-95543.55</t>
+          <t>-95543.76</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>logBF = -0.14 ± 0.50</t>
+          <t>quasi-logBF = -0.44 ± 0.50</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bayes factor</t>
-        </is>
-      </c>
+          <t>Descriptive quasi-Bayes factor</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B_12 = 0.8670 (inconclusive)</t>
+          <t>B_12 = 0.6432 (inconclusive); not exact count-data evidence</t>
         </is>
       </c>
     </row>
@@ -2150,9 +2155,10 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.995377</t>
-        </is>
-      </c>
+          <t>0.995346</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2181,17 +2187,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>logZ</t>
+          <t>quasi-logZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>-95543.55 ± 0.37</t>
+          <t>-95543.76 ± 0.36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-95543.41 ± 0.34</t>
+          <t>-95543.32 ± 0.34</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2209,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>12063</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>9544</t>
+          <t>9499</t>
         </is>
       </c>
     </row>
@@ -2237,9 +2243,10 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2698</t>
-        </is>
-      </c>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2278,17 +2285,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.6086 [0.5975, 0.6206]</t>
+          <t>0.6094 [0.5975, 0.6207]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1.01 [1.00, 1.05]</t>
+          <t>1.01 [1.00, 1.06]</t>
         </is>
       </c>
     </row>
@@ -2300,17 +2307,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.5802 [0.5652, 0.5939]</t>
+          <t>0.5797 [0.5653, 0.5937]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3708.48 [73.36, 84645.80]</t>
+          <t>4549.75 [79.04, 83111.58]</t>
         </is>
       </c>
     </row>
@@ -2387,9 +2394,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>kappa=0.5802, beta=3708, b=4.15e-05</t>
-        </is>
-      </c>
+          <t>kappa=0.5797, beta=4550, b=4.21e-05</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2407,6 +2416,7 @@
           <t>4PL fit = 0.9992; R2 limit = 0.9951</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2424,6 +2434,7 @@
           <t>4PL B = 1.014</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2433,12 +2444,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>max = 39.6%</t>
+          <t>max = 40.7%</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2545,7 +2556,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0.000035</t>
+          <t>0.000043</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2587,7 +2598,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0.000068</t>
+          <t>0.000075</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2629,7 +2640,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0.000101</t>
+          <t>0.000108</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2671,7 +2682,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.000362</t>
+          <t>0.000370</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2713,7 +2724,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.000689</t>
+          <t>0.000698</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2755,7 +2766,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.003303</t>
+          <t>0.003317</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2797,7 +2808,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.006563</t>
+          <t>0.006584</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2839,7 +2850,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0.032346</t>
+          <t>0.032422</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2849,7 +2860,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0.0329</t>
+          <t>0.0330</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2892,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0.063827</t>
+          <t>0.063970</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2891,7 +2902,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0.0660</t>
+          <t>0.0661</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2934,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.284399</t>
+          <t>0.285021</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2933,7 +2944,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.3346</t>
+          <t>0.3355</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2976,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.483209</t>
+          <t>0.484184</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2975,7 +2986,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.6601</t>
+          <t>0.6620</t>
         </is>
       </c>
     </row>
@@ -3031,12 +3042,12 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Exact_low</t>
+          <t>BetaQ_low</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Exact_up</t>
+          <t>BetaQ_up</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -3061,28 +3072,28 @@
         <v>5.646835443037974e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>12.97885741981815</v>
+        <v>12.97887109343666</v>
       </c>
       <c r="E2" t="n">
-        <v>158.6840953429565</v>
+        <v>158.6839112846045</v>
       </c>
       <c r="F2" t="n">
-        <v>-27.38735049369058</v>
+        <v>-27.38733252610769</v>
       </c>
       <c r="G2" t="n">
-        <v>53.34506533332687</v>
+        <v>53.34507471298101</v>
       </c>
       <c r="H2" t="n">
-        <v>6.316892518081884e-07</v>
+        <v>6.316891846121036e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>81.55605751090091</v>
+        <v>81.55606388969572</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>69.80815497544191</v>
+        <v>69.80816260378221</v>
       </c>
     </row>
     <row r="3">
@@ -3096,28 +3107,28 @@
         <v>9.41139240506329e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>36.76147582315897</v>
+        <v>36.76148696697198</v>
       </c>
       <c r="E3" t="n">
-        <v>72.32850251948926</v>
+        <v>72.32847289999501</v>
       </c>
       <c r="F3" t="n">
-        <v>-15.35205549610907</v>
+        <v>-15.35203880870757</v>
       </c>
       <c r="G3" t="n">
-        <v>88.87500714242702</v>
+        <v>88.87501274265153</v>
       </c>
       <c r="H3" t="n">
-        <v>6.316892518081884e-07</v>
+        <v>6.316891846121036e-07</v>
       </c>
       <c r="I3" t="n">
-        <v>116.0544356357358</v>
+        <v>116.0544383447384</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>105.0916305625737</v>
+        <v>105.0916344377673</v>
       </c>
     </row>
     <row r="4">
@@ -3131,28 +3142,28 @@
         <v>0.0004141012658227847</v>
       </c>
       <c r="D4" t="n">
-        <v>238.9498912917208</v>
+        <v>238.9498809276743</v>
       </c>
       <c r="E4" t="n">
-        <v>23.34486758059103</v>
+        <v>23.34486610981954</v>
       </c>
       <c r="F4" t="n">
-        <v>129.6181303416051</v>
+        <v>129.618131607749</v>
       </c>
       <c r="G4" t="n">
-        <v>348.2816522418366</v>
+        <v>348.2816302475996</v>
       </c>
       <c r="H4" t="n">
-        <v>141.2755168945061</v>
+        <v>141.2755169205803</v>
       </c>
       <c r="I4" t="n">
-        <v>373.4376846503316</v>
+        <v>373.4376599800934</v>
       </c>
       <c r="J4" t="n">
-        <v>144.2862817489761</v>
+        <v>144.2862814547834</v>
       </c>
       <c r="K4" t="n">
-        <v>364.011906858509</v>
+        <v>364.0118831910655</v>
       </c>
     </row>
     <row r="5">
@@ -3166,28 +3177,28 @@
         <v>0.00071526582278481</v>
       </c>
       <c r="D5" t="n">
-        <v>429.304004807714</v>
+        <v>429.3039741947516</v>
       </c>
       <c r="E5" t="n">
-        <v>17.07965933444543</v>
+        <v>17.07965873551523</v>
       </c>
       <c r="F5" t="n">
-        <v>285.5922689937429</v>
+        <v>285.5922536681485</v>
       </c>
       <c r="G5" t="n">
-        <v>573.0157406216849</v>
+        <v>573.0156947213547</v>
       </c>
       <c r="H5" t="n">
-        <v>297.163854159655</v>
+        <v>297.1638376030692</v>
       </c>
       <c r="I5" t="n">
-        <v>597.7083548459827</v>
+        <v>597.7083063189826</v>
       </c>
       <c r="J5" t="n">
-        <v>300.4022585885866</v>
+        <v>300.4022416876621</v>
       </c>
       <c r="K5" t="n">
-        <v>588.6335122027474</v>
+        <v>588.633464640799</v>
       </c>
     </row>
     <row r="6">
@@ -3201,28 +3212,28 @@
         <v>0.004461</v>
       </c>
       <c r="D6" t="n">
-        <v>2801.639068342863</v>
+        <v>2801.638785372164</v>
       </c>
       <c r="E6" t="n">
-        <v>6.548318899316022</v>
+        <v>6.548318864129389</v>
       </c>
       <c r="F6" t="n">
-        <v>2442.063564966813</v>
+        <v>2442.063320246038</v>
       </c>
       <c r="G6" t="n">
-        <v>3161.214571718912</v>
+        <v>3161.214250498289</v>
       </c>
       <c r="H6" t="n">
-        <v>2453.457054187353</v>
+        <v>2453.456808254606</v>
       </c>
       <c r="I6" t="n">
-        <v>3185.040568861354</v>
+        <v>3185.040245106281</v>
       </c>
       <c r="J6" t="n">
-        <v>2457.158521223922</v>
+        <v>2457.15827489724</v>
       </c>
       <c r="K6" t="n">
-        <v>3176.633369595049</v>
+        <v>3176.633046734165</v>
       </c>
     </row>
     <row r="7">
@@ -3236,28 +3247,28 @@
         <v>0.007246772151898733</v>
       </c>
       <c r="D7" t="n">
-        <v>4571.783700599189</v>
+        <v>4571.78322932903</v>
       </c>
       <c r="E7" t="n">
-        <v>5.121781038887794</v>
+        <v>5.121781022022363</v>
       </c>
       <c r="F7" t="n">
-        <v>4112.844902458412</v>
+        <v>4112.84448000797</v>
       </c>
       <c r="G7" t="n">
-        <v>5030.722498739966</v>
+        <v>5030.721978650091</v>
       </c>
       <c r="H7" t="n">
-        <v>4124.211296775599</v>
+        <v>4124.210873116052</v>
       </c>
       <c r="I7" t="n">
-        <v>5054.448605271643</v>
+        <v>5054.448082657811</v>
       </c>
       <c r="J7" t="n">
-        <v>4127.99707368848</v>
+        <v>4127.996649626092</v>
       </c>
       <c r="K7" t="n">
-        <v>5046.129104919044</v>
+        <v>5046.128583190922</v>
       </c>
     </row>
     <row r="8">
@@ -3271,28 +3282,28 @@
         <v>0.0336363164556962</v>
       </c>
       <c r="D8" t="n">
-        <v>21591.05246744605</v>
+        <v>21591.05018574738</v>
       </c>
       <c r="E8" t="n">
-        <v>2.368182324427366</v>
+        <v>2.368182322776154</v>
       </c>
       <c r="F8" t="n">
-        <v>20588.89252585242</v>
+        <v>20588.89035075873</v>
       </c>
       <c r="G8" t="n">
-        <v>22593.21240903969</v>
+        <v>22593.21002073602</v>
       </c>
       <c r="H8" t="n">
-        <v>20600.20185574262</v>
+        <v>20600.19967944592</v>
       </c>
       <c r="I8" t="n">
-        <v>22616.99868177794</v>
+        <v>22616.99629094397</v>
       </c>
       <c r="J8" t="n">
-        <v>20604.32273331299</v>
+        <v>20604.32055657834</v>
       </c>
       <c r="K8" t="n">
-        <v>22608.76244279254</v>
+        <v>22608.76005283308</v>
       </c>
     </row>
     <row r="9">
@@ -3306,28 +3317,28 @@
         <v>0.07596875949367088</v>
       </c>
       <c r="D9" t="n">
-        <v>49887.79812196436</v>
+        <v>49887.79283019299</v>
       </c>
       <c r="E9" t="n">
-        <v>1.575197041941002</v>
+        <v>1.575197041465666</v>
       </c>
       <c r="F9" t="n">
-        <v>48347.5974282325</v>
+        <v>48347.59230030032</v>
       </c>
       <c r="G9" t="n">
-        <v>51427.99881569621</v>
+        <v>51427.99336008565</v>
       </c>
       <c r="H9" t="n">
-        <v>48358.88189545009</v>
+        <v>48358.87676631756</v>
       </c>
       <c r="I9" t="n">
-        <v>51452.2607090166</v>
+        <v>51452.25525082538</v>
       </c>
       <c r="J9" t="n">
-        <v>48363.40767753696</v>
+        <v>48363.40254792167</v>
       </c>
       <c r="K9" t="n">
-        <v>51443.89101658273</v>
+        <v>51443.88555928121</v>
       </c>
     </row>
     <row r="10">
@@ -3341,28 +3352,28 @@
         <v>0.2942754177215189</v>
       </c>
       <c r="D10" t="n">
-        <v>220144.9758572677</v>
+        <v>220144.9524543512</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8039066566617648</v>
+        <v>0.8039066566067905</v>
       </c>
       <c r="F10" t="n">
-        <v>216676.3097701552</v>
+        <v>216676.2867362187</v>
       </c>
       <c r="G10" t="n">
-        <v>223613.6419443803</v>
+        <v>223613.6181724836</v>
       </c>
       <c r="H10" t="n">
-        <v>216687.4996129229</v>
+        <v>216687.4765777963</v>
       </c>
       <c r="I10" t="n">
-        <v>223641.7196354076</v>
+        <v>223641.6958605255</v>
       </c>
       <c r="J10" t="n">
-        <v>216694.6830567234</v>
+        <v>216694.6600208374</v>
       </c>
       <c r="K10" t="n">
-        <v>223632.0683908191</v>
+        <v>223632.0446169621</v>
       </c>
     </row>
     <row r="11">
@@ -3376,28 +3387,28 @@
         <v>0.4674826835443037</v>
       </c>
       <c r="D11" t="n">
-        <v>398038.6908533297</v>
+        <v>398038.6485269296</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6451276278636928</v>
+        <v>0.6451276278392932</v>
       </c>
       <c r="F11" t="n">
-        <v>393005.7825099087</v>
+        <v>393005.7407188853</v>
       </c>
       <c r="G11" t="n">
-        <v>403071.5991967508</v>
+        <v>403071.5563349738</v>
       </c>
       <c r="H11" t="n">
-        <v>393016.8547464615</v>
+        <v>393016.8129542603</v>
       </c>
       <c r="I11" t="n">
-        <v>403105.0181619717</v>
+        <v>403104.9752966397</v>
       </c>
       <c r="J11" t="n">
-        <v>393027.6605513578</v>
+        <v>393027.6187580089</v>
       </c>
       <c r="K11" t="n">
-        <v>403093.538234174</v>
+        <v>403093.4953700695</v>
       </c>
     </row>
   </sheetData>
@@ -3438,7 +3449,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5792580654246042</v>
+        <v>0.5792578974306756</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3453,7 +3464,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.592348888054933e-05</v>
+        <v>3.592346505010824e-05</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3468,7 +3479,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6332087338310581</v>
+        <v>0.6332088011887854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3483,7 +3494,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9950506598703104</v>
+        <v>0.9950506588285759</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3498,7 +3509,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.999224654458707</v>
+        <v>0.9992245976545764</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3528,7 +3539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.014036692085916</v>
+        <v>1.014002714423583</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -3543,7 +3554,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.86185747053582</v>
+        <v>3.86350525392808</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -3558,7 +3569,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.981063765234317</v>
+        <v>2.981985160958645</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -3577,7 +3588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3624,16 +3635,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.014036692085916</v>
+        <v>1.014002714423583</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9692900361476653</v>
+        <v>0.9705408579601797</v>
       </c>
       <c r="E2" t="n">
-        <v>1.075189400581873</v>
+        <v>1.076792310861186</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1044334640557905</v>
+        <v>0.1047841898149214</v>
       </c>
     </row>
     <row r="3">
@@ -3648,16 +3659,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.86185747053582</v>
+        <v>3.86350525392808</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9489056189304</v>
+        <v>1.891486536936102</v>
       </c>
       <c r="E3" t="n">
         <v>21.07700000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>4.953081393347136</v>
+        <v>4.965830819967882</v>
       </c>
     </row>
     <row r="4">
@@ -3672,16 +3683,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2.981063765234317</v>
+        <v>2.981985160958645</v>
       </c>
       <c r="D4" t="n">
-        <v>1.784817920233955</v>
+        <v>1.716915827905592</v>
       </c>
       <c r="E4" t="n">
-        <v>14.36018951121924</v>
+        <v>14.37109502598155</v>
       </c>
       <c r="F4" t="n">
-        <v>4.218417511775981</v>
+        <v>4.24354197457103</v>
       </c>
     </row>
     <row r="5">
@@ -3696,16 +3707,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.5792580654246042</v>
+        <v>0.5792578974306756</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3467238353647154</v>
+        <v>0.3467244683402124</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6634877384029494</v>
+        <v>0.6634878041061314</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5468441821453822</v>
+        <v>0.5468433614300936</v>
       </c>
     </row>
     <row r="6">
@@ -3720,16 +3731,50 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3.592348888054933e-05</v>
+        <v>3.592346505010824e-05</v>
       </c>
       <c r="D6" t="n">
-        <v>1.74467703002305e-05</v>
+        <v>1.744678591383044e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0002198203647049955</v>
+        <v>0.0002198204794302141</v>
       </c>
       <c r="F6" t="n">
-        <v>5.633461579349538</v>
+        <v>5.63346807536802</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Case resampling</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4PL</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10 nonzero concentration means</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Case resampling</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>All 11 points, including the blank</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3785,7 +3830,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.3294783427576616</v>
+        <v>-0.3351784080097026</v>
       </c>
     </row>
     <row r="3">
@@ -3805,7 +3850,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.2405323271024501</v>
+        <v>-0.2487899084543067</v>
       </c>
     </row>
     <row r="4">
@@ -3825,7 +3870,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9793185936621591</v>
+        <v>0.9800941479257016</v>
       </c>
     </row>
     <row r="5">
@@ -3845,7 +3890,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2043011787696224</v>
+        <v>0.203834434726683</v>
       </c>
     </row>
   </sheetData>
@@ -3896,16 +3941,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.87014561530478</v>
+        <v>24.8701580239877</v>
       </c>
       <c r="C2" t="n">
-        <v>24.86965605308483</v>
+        <v>24.86966846128267</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4129881370857652</v>
+        <v>0.4129883431416091</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4129800075238264</v>
+        <v>0.4129802135716151</v>
       </c>
     </row>
     <row r="3">
@@ -3915,16 +3960,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>86.15004392198102</v>
+        <v>86.15004981203893</v>
       </c>
       <c r="C3" t="n">
-        <v>54.0441140290386</v>
+        <v>54.04409035391001</v>
       </c>
       <c r="D3" t="n">
-        <v>1.430588573928612</v>
+        <v>1.430588671737611</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8974446036040949</v>
+        <v>0.897444210460146</v>
       </c>
     </row>
     <row r="4">
@@ -3934,16 +3979,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>318.5253385869473</v>
+        <v>318.5252915203518</v>
       </c>
       <c r="C4" t="n">
-        <v>318.2945941316083</v>
+        <v>318.2945471031751</v>
       </c>
       <c r="D4" t="n">
-        <v>5.289361318282087</v>
+        <v>5.289360536704613</v>
       </c>
       <c r="E4" t="n">
-        <v>5.285529626894856</v>
+        <v>5.285528845951098</v>
       </c>
     </row>
     <row r="5">
@@ -3953,10 +3998,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8056159.771009704</v>
+        <v>8056158.914033951</v>
       </c>
       <c r="D5" t="n">
-        <v>133778.8072236749</v>
+        <v>133778.7929929251</v>
       </c>
     </row>
   </sheetData>
@@ -3997,10 +4042,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6332087338310581</v>
+        <v>0.6332088011887854</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7040896945013125</v>
+        <v>0.7040896947830023</v>
       </c>
     </row>
     <row r="3">
@@ -4010,10 +4055,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5792580654246042</v>
+        <v>0.5792578974306756</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4202735927107593</v>
+        <v>0.4202735921425409</v>
       </c>
     </row>
     <row r="4">
@@ -4026,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>11.19393288235434</v>
+        <v>11.19392109856104</v>
       </c>
     </row>
   </sheetData>
@@ -4051,7 +4096,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>logL (binomial)</t>
+          <t>quasi-logL (binomial-form)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -4066,7 +4111,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ΔlogL</t>
+          <t>Δ quasi-logL</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -4080,16 +4125,16 @@
         <v>0.7</v>
       </c>
       <c r="B2" t="n">
-        <v>-95991.8442009264</v>
+        <v>-95991.84420099526</v>
       </c>
       <c r="C2" t="n">
-        <v>1.347791647431853</v>
+        <v>1.347792456318551</v>
       </c>
       <c r="D2" t="n">
-        <v>0.449865890450673</v>
+        <v>0.449866317864492</v>
       </c>
       <c r="E2" t="n">
-        <v>-580.4385020537738</v>
+        <v>-580.4385156039934</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -4102,16 +4147,16 @@
         <v>0.8</v>
       </c>
       <c r="B3" t="n">
-        <v>-95787.20035054567</v>
+        <v>-95787.20035054485</v>
       </c>
       <c r="C3" t="n">
-        <v>1.281318463751849</v>
+        <v>1.281318312029158</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5604359416304648</v>
+        <v>0.5604362984020155</v>
       </c>
       <c r="E3" t="n">
-        <v>-375.7946516730444</v>
+        <v>-375.7946651535894</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -4124,16 +4169,16 @@
         <v>0.9</v>
       </c>
       <c r="B4" t="n">
-        <v>-95665.40695831274</v>
+        <v>-95665.40695831414</v>
       </c>
       <c r="C4" t="n">
-        <v>1.232830510827905</v>
+        <v>1.232830581586678</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6785326875208941</v>
+        <v>0.6785326158945628</v>
       </c>
       <c r="E4" t="n">
-        <v>-254.0012594401196</v>
+        <v>-254.0012729228765</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -4146,16 +4191,16 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>-95588.6761397544</v>
+        <v>-95588.67613975451</v>
       </c>
       <c r="C5" t="n">
-        <v>1.196144954930925</v>
+        <v>1.196145049577353</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8027856330185281</v>
+        <v>0.8027855373386319</v>
       </c>
       <c r="E5" t="n">
-        <v>-177.2704408817808</v>
+        <v>-177.2704543632426</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -4168,16 +4213,16 @@
         <v>1.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-95449.22850622964</v>
+        <v>-95449.22850622975</v>
       </c>
       <c r="C6" t="n">
-        <v>1.097155118821785</v>
+        <v>1.097155061643494</v>
       </c>
       <c r="D6" t="n">
-        <v>1.489892340525915</v>
+        <v>1.489892443432991</v>
       </c>
       <c r="E6" t="n">
-        <v>-37.82280735702079</v>
+        <v>-37.82282083848258</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -4190,20 +4235,20 @@
         <v>2</v>
       </c>
       <c r="B7" t="n">
-        <v>-95420.06860746644</v>
+        <v>-95420.06860746662</v>
       </c>
       <c r="C7" t="n">
-        <v>1.053548142682606</v>
+        <v>1.053548069680348</v>
       </c>
       <c r="D7" t="n">
-        <v>2.24963446299648</v>
+        <v>2.249634950778145</v>
       </c>
       <c r="E7" t="n">
-        <v>-8.662908593818429</v>
+        <v>-8.662922075352981</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>within 2σ but data cannot resolve</t>
+          <t>broader profile-quasi deviation; data cannot resolve</t>
         </is>
       </c>
     </row>
@@ -4212,20 +4257,20 @@
         <v>2.9189</v>
       </c>
       <c r="B8" t="n">
-        <v>-95411.42136332132</v>
+        <v>-95411.42136338726</v>
       </c>
       <c r="C8" t="n">
-        <v>1.015658905225033</v>
+        <v>1.015659230838894</v>
       </c>
       <c r="D8" t="n">
-        <v>3.756482967989188</v>
+        <v>3.756479669361889</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.01566444869968109</v>
+        <v>-0.01567799599433783</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MLE neighbor (1σ)</t>
+          <t>quasi-MLE neighbor</t>
         </is>
       </c>
     </row>
@@ -4234,20 +4279,20 @@
         <v>3</v>
       </c>
       <c r="B9" t="n">
-        <v>-95411.40686229018</v>
+        <v>-95411.40686228976</v>
       </c>
       <c r="C9" t="n">
-        <v>1.013519766206536</v>
+        <v>1.013519706692497</v>
       </c>
       <c r="D9" t="n">
-        <v>3.894422930737452</v>
+        <v>3.894423606842069</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.001163417560746893</v>
+        <v>-0.001176898498670198</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MLE neighbor (1σ)</t>
+          <t>quasi-MLE neighbor</t>
         </is>
       </c>
     </row>
@@ -4256,20 +4301,20 @@
         <v>4</v>
       </c>
       <c r="B10" t="n">
-        <v>-95413.48865062537</v>
+        <v>-95413.48865062535</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9947538923695216</v>
+        <v>0.994753944241444</v>
       </c>
       <c r="D10" t="n">
-        <v>5.641394818717172</v>
+        <v>5.641394163233278</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.08295175274543</v>
+        <v>-2.082965234090807</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>within 1σ formal 95% CI</t>
+          <t>within nominal 95% profile-quasi interval</t>
         </is>
       </c>
     </row>
@@ -4278,20 +4323,20 @@
         <v>5</v>
       </c>
       <c r="B11" t="n">
-        <v>-95416.53224755899</v>
+        <v>-95416.5322475858</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9838713330512912</v>
+        <v>0.9838707851204802</v>
       </c>
       <c r="D11" t="n">
-        <v>7.454100300922473</v>
+        <v>7.454113467511976</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.12654868637037</v>
+        <v>-5.126562194534927</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>within 2σ but data cannot resolve</t>
+          <t>broader profile-quasi deviation; data cannot resolve</t>
         </is>
       </c>
     </row>
@@ -4300,20 +4345,20 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>-95426.25687146299</v>
+        <v>-95426.25687148017</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9629157423926308</v>
+        <v>0.9629192234386558</v>
       </c>
       <c r="D12" t="n">
-        <v>17.05926767063373</v>
+        <v>17.05901564127476</v>
       </c>
       <c r="E12" t="n">
-        <v>-14.85117259036633</v>
+        <v>-14.85118608891207</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>within 2σ but data cannot resolve</t>
+          <t>broader profile-quasi deviation; data cannot resolve</t>
         </is>
       </c>
     </row>
@@ -4322,20 +4367,20 @@
         <v>20</v>
       </c>
       <c r="B13" t="n">
-        <v>-95432.78058780686</v>
+        <v>-95432.78058753665</v>
       </c>
       <c r="C13" t="n">
-        <v>0.952832910178592</v>
+        <v>0.9528286139060813</v>
       </c>
       <c r="D13" t="n">
-        <v>37.54415043373916</v>
+        <v>37.5449373694756</v>
       </c>
       <c r="E13" t="n">
-        <v>-21.3748889342387</v>
+        <v>-21.37490214538411</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>within 2σ but data cannot resolve</t>
+          <t>broader profile-quasi deviation; data cannot resolve</t>
         </is>
       </c>
     </row>
@@ -4344,20 +4389,20 @@
         <v>30</v>
       </c>
       <c r="B14" t="n">
-        <v>-95435.18314334184</v>
+        <v>-95435.18314207626</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9495149883009555</v>
+        <v>0.9495222382467593</v>
       </c>
       <c r="D14" t="n">
-        <v>58.88197214509258</v>
+        <v>58.88009214114768</v>
       </c>
       <c r="E14" t="n">
-        <v>-23.77744446921861</v>
+        <v>-23.77745668499847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>within 2σ but data cannot resolve</t>
+          <t>broader profile-quasi deviation; data cannot resolve</t>
         </is>
       </c>
     </row>
@@ -4366,20 +4411,20 @@
         <v>40</v>
       </c>
       <c r="B15" t="n">
-        <v>-95436.42572008763</v>
+        <v>-95436.42571718479</v>
       </c>
       <c r="C15" t="n">
-        <v>0.947867987846393</v>
+        <v>0.9478795867696195</v>
       </c>
       <c r="D15" t="n">
-        <v>80.74253205178181</v>
+        <v>80.737366810542</v>
       </c>
       <c r="E15" t="n">
-        <v>-25.02002121500846</v>
+        <v>-25.02003179352323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>within 2σ but data cannot resolve</t>
+          <t>broader profile-quasi deviation; data cannot resolve</t>
         </is>
       </c>
     </row>
@@ -4388,20 +4433,20 @@
         <v>50</v>
       </c>
       <c r="B16" t="n">
-        <v>-95437.18431060575</v>
+        <v>-95437.1842980113</v>
       </c>
       <c r="C16" t="n">
-        <v>0.946873079491881</v>
+        <v>0.9468891936794671</v>
       </c>
       <c r="D16" t="n">
-        <v>102.9900417811858</v>
+        <v>102.9802746032763</v>
       </c>
       <c r="E16" t="n">
-        <v>-25.77861173312704</v>
+        <v>-25.77861262003717</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>within 2σ but data cannot resolve</t>
+          <t>broader profile-quasi deviation; data cannot resolve</t>
         </is>
       </c>
     </row>
@@ -4410,20 +4455,20 @@
         <v>60</v>
       </c>
       <c r="B17" t="n">
-        <v>-95437.69541117508</v>
+        <v>-95437.69541520005</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9462564293297833</v>
+        <v>0.9462536818810428</v>
       </c>
       <c r="D17" t="n">
-        <v>125.5056619213914</v>
+        <v>125.5092470861488</v>
       </c>
       <c r="E17" t="n">
-        <v>-26.28971230245952</v>
+        <v>-26.28972980879189</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>within 2σ but data cannot resolve</t>
+          <t>broader profile-quasi deviation; data cannot resolve</t>
         </is>
       </c>
     </row>
@@ -4432,20 +4477,20 @@
         <v>70</v>
       </c>
       <c r="B18" t="n">
-        <v>-95438.06312144491</v>
+        <v>-95438.06311315749</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9457895961835514</v>
+        <v>0.9457848983966246</v>
       </c>
       <c r="D18" t="n">
-        <v>148.2889311314053</v>
+        <v>148.2951745665793</v>
       </c>
       <c r="E18" t="n">
-        <v>-26.65742257228703</v>
+        <v>-26.65742776622938</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>within 2σ but data cannot resolve</t>
+          <t>broader profile-quasi deviation; data cannot resolve</t>
         </is>
       </c>
     </row>
@@ -4454,20 +4499,20 @@
         <v>80</v>
       </c>
       <c r="B19" t="n">
-        <v>-95438.34033873949</v>
+        <v>-95438.34038786835</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9454000712975834</v>
+        <v>0.9454746957790328</v>
       </c>
       <c r="D19" t="n">
-        <v>171.3328331197461</v>
+        <v>171.2503995446615</v>
       </c>
       <c r="E19" t="n">
-        <v>-26.93463986687129</v>
+        <v>-26.93470247708319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>within 2σ but data cannot resolve</t>
+          <t>broader profile-quasi deviation; data cannot resolve</t>
         </is>
       </c>
     </row>
@@ -4476,20 +4521,20 @@
         <v>90</v>
       </c>
       <c r="B20" t="n">
-        <v>-95438.55678598055</v>
+        <v>-95438.55678257965</v>
       </c>
       <c r="C20" t="n">
-        <v>0.9451352791106074</v>
+        <v>0.9451435103501377</v>
       </c>
       <c r="D20" t="n">
-        <v>194.5167587546605</v>
+        <v>194.5081636700537</v>
       </c>
       <c r="E20" t="n">
-        <v>-27.15108710792265</v>
+        <v>-27.15109718838357</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>within 2σ but data cannot resolve</t>
+          <t>broader profile-quasi deviation; data cannot resolve</t>
         </is>
       </c>
     </row>
@@ -4498,20 +4543,20 @@
         <v>100</v>
       </c>
       <c r="B21" t="n">
-        <v>-95438.73047820271</v>
+        <v>-95438.73047360675</v>
       </c>
       <c r="C21" t="n">
-        <v>0.9449382610557168</v>
+        <v>0.9449311370627688</v>
       </c>
       <c r="D21" t="n">
-        <v>217.8400412725188</v>
+        <v>217.8521986220176</v>
       </c>
       <c r="E21" t="n">
-        <v>-27.3247793300834</v>
+        <v>-27.32478821548284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>within 2σ but data cannot resolve</t>
+          <t>broader profile-quasi deviation; data cannot resolve</t>
         </is>
       </c>
     </row>
@@ -4520,20 +4565,20 @@
         <v>200</v>
       </c>
       <c r="B22" t="n">
-        <v>-95439.51794072971</v>
+        <v>-95439.51794319649</v>
       </c>
       <c r="C22" t="n">
-        <v>0.9439574782526134</v>
+        <v>0.9439447046922613</v>
       </c>
       <c r="D22" t="n">
-        <v>457.9487040409425</v>
+        <v>457.9866420684186</v>
       </c>
       <c r="E22" t="n">
-        <v>-28.11224185708852</v>
+        <v>-28.11225780523091</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>within 2σ but data cannot resolve</t>
+          <t>broader profile-quasi deviation; data cannot resolve</t>
         </is>
       </c>
     </row>
@@ -4542,20 +4587,20 @@
         <v>500</v>
       </c>
       <c r="B23" t="n">
-        <v>-95439.99501153007</v>
+        <v>-95439.99573550925</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9433644405445712</v>
+        <v>0.9432124675798149</v>
       </c>
       <c r="D23" t="n">
-        <v>1216.450217895359</v>
+        <v>1218.095630829385</v>
       </c>
       <c r="E23" t="n">
-        <v>-28.58931265745196</v>
+        <v>-28.59005011798581</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>within 2σ but data cannot resolve</t>
+          <t>broader profile-quasi deviation; data cannot resolve</t>
         </is>
       </c>
     </row>
@@ -4564,16 +4609,16 @@
         <v>1000</v>
       </c>
       <c r="B24" t="n">
-        <v>-95788.6221360263</v>
+        <v>-95788.39862437721</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8284722104629214</v>
+        <v>0.8285071986516402</v>
       </c>
       <c r="D24" t="n">
-        <v>8365.590298978541</v>
+        <v>8362.104779238993</v>
       </c>
       <c r="E24" t="n">
-        <v>-377.2164371536783</v>
+        <v>-376.9929389859462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4586,16 +4631,16 @@
         <v>10000</v>
       </c>
       <c r="B25" t="n">
-        <v>-95444.14972935295</v>
+        <v>-95444.15947757379</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9557795927761998</v>
+        <v>0.955796093058936</v>
       </c>
       <c r="D25" t="n">
-        <v>25287.66576231551</v>
+        <v>25283.02844713182</v>
       </c>
       <c r="E25" t="n">
-        <v>-32.74403048033128</v>
+        <v>-32.75379218252783</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -4606,21 +4651,21 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BEST (MLE)</t>
+          <t>BEST (quasi-MLE)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.014036692085916</v>
+        <v>1.014002714423583</v>
       </c>
       <c r="D27" t="n">
-        <v>3.86185747053582</v>
+        <v>3.86350525392808</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>ΔlogL=0 reference</t>
+          <t>Δ quasi-logL=0 reference</t>
         </is>
       </c>
     </row>
@@ -4668,15 +4713,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Deviance (binomial)</t>
+          <t>Deviance (binomial-form quasi)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.01559152022550335</v>
+        <v>0.01557254909866553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Reject normality — overfit signature</t>
+          <t>Reject normality in this quasi-deviance diagnostic</t>
         </is>
       </c>
     </row>
@@ -4688,15 +4733,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Deviance (binomial)</t>
+          <t>Deviance (binomial-form quasi)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.186936570461376</v>
+        <v>0.1869345840779973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cannot reject (consistent with model)</t>
+          <t>Cannot reject normality in this diagnostic</t>
         </is>
       </c>
     </row>
